--- a/docs/downloads/my_mp_history.xlsx
+++ b/docs/downloads/my_mp_history.xlsx
@@ -524,13 +524,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>148700</v>
+        <v>147200</v>
       </c>
       <c r="F3" t="n">
         <v>672</v>
       </c>
       <c r="G3" t="n">
-        <v>99926400</v>
+        <v>98918400</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>8600</v>
+        <v>8590</v>
       </c>
       <c r="F5" t="n">
         <v>11628</v>
       </c>
       <c r="G5" t="n">
-        <v>100000800</v>
+        <v>99884520</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -620,13 +620,13 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>58300</v>
+        <v>58700</v>
       </c>
       <c r="F6" t="n">
         <v>1715</v>
       </c>
       <c r="G6" t="n">
-        <v>99984500</v>
+        <v>100670500</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -652,13 +652,13 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>48900</v>
+        <v>49000</v>
       </c>
       <c r="F7" t="n">
         <v>2045</v>
       </c>
       <c r="G7" t="n">
-        <v>100000500</v>
+        <v>100205000</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -684,13 +684,13 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>14780</v>
+        <v>14600</v>
       </c>
       <c r="F8" t="n">
         <v>6766</v>
       </c>
       <c r="G8" t="n">
-        <v>100001480</v>
+        <v>98783600</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -716,13 +716,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3915</v>
+        <v>4035</v>
       </c>
       <c r="F9" t="n">
         <v>12771</v>
       </c>
       <c r="G9" t="n">
-        <v>49998465</v>
+        <v>51530985</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -748,13 +748,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>98700</v>
+        <v>99100</v>
       </c>
       <c r="F10" t="n">
         <v>1013</v>
       </c>
       <c r="G10" t="n">
-        <v>99983100</v>
+        <v>100388300</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>

--- a/docs/downloads/my_mp_history.xlsx
+++ b/docs/downloads/my_mp_history.xlsx
@@ -591,10 +591,10 @@
         <v>8590</v>
       </c>
       <c r="F5" t="n">
-        <v>11628</v>
+        <v>11579</v>
       </c>
       <c r="G5" t="n">
-        <v>99884520</v>
+        <v>99463610</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>

--- a/docs/downloads/my_mp_history.xlsx
+++ b/docs/downloads/my_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,49 +473,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>탑코미디어</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>134580</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>248500</v>
+        <v>3750</v>
       </c>
       <c r="F2" t="n">
-        <v>604</v>
+        <v>12771</v>
       </c>
       <c r="G2" t="n">
-        <v>150094000</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
+        <v>47891250</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-7.06</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -524,13 +526,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>147200</v>
+        <v>72000</v>
       </c>
       <c r="F3" t="n">
-        <v>672</v>
+        <v>665.1562</v>
       </c>
       <c r="G3" t="n">
-        <v>98918400</v>
+        <v>47891250</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
@@ -542,12 +544,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>롯데쇼핑</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>023530</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -556,13 +558,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>115300</v>
+        <v>248500</v>
       </c>
       <c r="F4" t="n">
-        <v>867</v>
+        <v>604</v>
       </c>
       <c r="G4" t="n">
-        <v>99965100</v>
+        <v>150094000</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
@@ -574,12 +576,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SFA반도체</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>036540</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -588,13 +590,13 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>8590</v>
+        <v>147200</v>
       </c>
       <c r="F5" t="n">
-        <v>11579</v>
+        <v>672</v>
       </c>
       <c r="G5" t="n">
-        <v>99463610</v>
+        <v>98918400</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -606,12 +608,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>인바디</t>
+          <t>롯데쇼핑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>041830</t>
+          <t>023530</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -620,13 +622,13 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>58700</v>
+        <v>115300</v>
       </c>
       <c r="F6" t="n">
-        <v>1715</v>
+        <v>867</v>
       </c>
       <c r="G6" t="n">
-        <v>100670500</v>
+        <v>99965100</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -638,12 +640,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>SFA반도체</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>089970</t>
+          <t>036540</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -652,13 +654,13 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>49000</v>
+        <v>8590</v>
       </c>
       <c r="F7" t="n">
-        <v>2045</v>
+        <v>11579</v>
       </c>
       <c r="G7" t="n">
-        <v>100205000</v>
+        <v>99463610</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -670,12 +672,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>인바디</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>041830</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -684,13 +686,13 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>14600</v>
+        <v>58700</v>
       </c>
       <c r="F8" t="n">
-        <v>6766</v>
+        <v>1715</v>
       </c>
       <c r="G8" t="n">
-        <v>98783600</v>
+        <v>100670500</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -702,12 +704,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>탑코미디어</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>134580</t>
+          <t>089970</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -716,13 +718,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4035</v>
+        <v>49000</v>
       </c>
       <c r="F9" t="n">
-        <v>12771</v>
+        <v>2045</v>
       </c>
       <c r="G9" t="n">
-        <v>51530985</v>
+        <v>100205000</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -734,12 +736,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>420770</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -748,13 +750,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>99100</v>
+        <v>14600</v>
       </c>
       <c r="F10" t="n">
-        <v>1013</v>
+        <v>6766</v>
       </c>
       <c r="G10" t="n">
-        <v>100388300</v>
+        <v>98783600</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -766,29 +768,93 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>탑코미디어</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>134580</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4035</v>
+      </c>
+      <c r="F11" t="n">
+        <v>12771</v>
+      </c>
+      <c r="G11" t="n">
+        <v>51530985</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>기가비스</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>420770</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>99100</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1013</v>
+      </c>
+      <c r="G12" t="n">
+        <v>100388300</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>달바글로벌</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>483650</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
         <v>163100</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F13" t="n">
         <v>613</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G13" t="n">
         <v>99980300</v>
       </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/my_mp_history.xlsx
+++ b/docs/downloads/my_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,147 +473,149 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>탑코미디어</t>
+          <t>메쥬</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>134580</t>
+          <t>0088M0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3750</v>
+        <v>14130</v>
       </c>
       <c r="F2" t="n">
-        <v>12771</v>
+        <v>3247.997</v>
       </c>
       <c r="G2" t="n">
-        <v>47891250</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-7.06</v>
-      </c>
+        <v>45894198</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>롯데쇼핑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>023530</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>72000</v>
+        <v>102200</v>
       </c>
       <c r="F3" t="n">
-        <v>665.1562</v>
+        <v>867</v>
       </c>
       <c r="G3" t="n">
-        <v>47891250</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>88607400</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-11.36</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>248500</v>
+        <v>13980</v>
       </c>
       <c r="F4" t="n">
-        <v>604</v>
+        <v>6766</v>
       </c>
       <c r="G4" t="n">
-        <v>150094000</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+        <v>94588680</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-4.25</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>147200</v>
+        <v>82900</v>
       </c>
       <c r="F5" t="n">
-        <v>672</v>
+        <v>553.6091</v>
       </c>
       <c r="G5" t="n">
-        <v>98918400</v>
+        <v>45894198</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>롯데쇼핑</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>023530</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -622,62 +624,64 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>115300</v>
+        <v>125800</v>
       </c>
       <c r="F6" t="n">
-        <v>867</v>
+        <v>728.773</v>
       </c>
       <c r="G6" t="n">
-        <v>99965100</v>
+        <v>91679642.09999999</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SFA반도체</t>
+          <t>탑코미디어</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>036540</t>
+          <t>134580</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>8590</v>
+        <v>3750</v>
       </c>
       <c r="F7" t="n">
-        <v>11579</v>
+        <v>12771</v>
       </c>
       <c r="G7" t="n">
-        <v>99463610</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
+        <v>47891250</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-7.06</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>인바디</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>041830</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -686,13 +690,13 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>58700</v>
+        <v>72000</v>
       </c>
       <c r="F8" t="n">
-        <v>1715</v>
+        <v>665.1562</v>
       </c>
       <c r="G8" t="n">
-        <v>100670500</v>
+        <v>47891250</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -704,12 +708,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>089970</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -718,13 +722,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>49000</v>
+        <v>248500</v>
       </c>
       <c r="F9" t="n">
-        <v>2045</v>
+        <v>604</v>
       </c>
       <c r="G9" t="n">
-        <v>100205000</v>
+        <v>150094000</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -736,12 +740,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -750,13 +754,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>14600</v>
+        <v>147200</v>
       </c>
       <c r="F10" t="n">
-        <v>6766</v>
+        <v>672</v>
       </c>
       <c r="G10" t="n">
-        <v>98783600</v>
+        <v>98918400</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -768,12 +772,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>탑코미디어</t>
+          <t>롯데쇼핑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>134580</t>
+          <t>023530</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -782,13 +786,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4035</v>
+        <v>115300</v>
       </c>
       <c r="F11" t="n">
-        <v>12771</v>
+        <v>867</v>
       </c>
       <c r="G11" t="n">
-        <v>51530985</v>
+        <v>99965100</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -800,12 +804,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>SFA반도체</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>420770</t>
+          <t>036540</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -814,13 +818,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>99100</v>
+        <v>8590</v>
       </c>
       <c r="F12" t="n">
-        <v>1013</v>
+        <v>11579</v>
       </c>
       <c r="G12" t="n">
-        <v>100388300</v>
+        <v>99463610</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -832,29 +836,189 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>인바디</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>041830</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>58700</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1715</v>
+      </c>
+      <c r="G13" t="n">
+        <v>100670500</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>브이엠</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>089970</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>49000</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2045</v>
+      </c>
+      <c r="G14" t="n">
+        <v>100205000</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>후성</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>093370</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>14600</v>
+      </c>
+      <c r="F15" t="n">
+        <v>6766</v>
+      </c>
+      <c r="G15" t="n">
+        <v>98783600</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>탑코미디어</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>134580</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4035</v>
+      </c>
+      <c r="F16" t="n">
+        <v>12771</v>
+      </c>
+      <c r="G16" t="n">
+        <v>51530985</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>기가비스</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>420770</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>99100</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1013</v>
+      </c>
+      <c r="G17" t="n">
+        <v>100388300</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>달바글로벌</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>483650</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
         <v>163100</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F18" t="n">
         <v>613</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G18" t="n">
         <v>99980300</v>
       </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/my_mp_history.xlsx
+++ b/docs/downloads/my_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,31 +510,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>롯데쇼핑</t>
+          <t>메쥬</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>023530</t>
+          <t>0088M0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102200</v>
+        <v>14130</v>
       </c>
       <c r="F3" t="n">
-        <v>867</v>
+        <v>55</v>
       </c>
       <c r="G3" t="n">
-        <v>88607400</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-11.36</v>
-      </c>
+        <v>777150</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -544,12 +542,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>롯데쇼핑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>023530</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -558,16 +556,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>13980</v>
+        <v>102200</v>
       </c>
       <c r="F4" t="n">
-        <v>6766</v>
+        <v>867</v>
       </c>
       <c r="G4" t="n">
-        <v>94588680</v>
+        <v>88607400</v>
       </c>
       <c r="H4" t="n">
-        <v>-4.25</v>
+        <v>-11.36</v>
       </c>
     </row>
     <row r="5">
@@ -578,29 +576,31 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>82900</v>
+        <v>13980</v>
       </c>
       <c r="F5" t="n">
-        <v>553.6091</v>
+        <v>6766</v>
       </c>
       <c r="G5" t="n">
-        <v>45894198</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>94588680</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-4.25</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -610,63 +610,61 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>125800</v>
+        <v>82900</v>
       </c>
       <c r="F6" t="n">
-        <v>728.773</v>
+        <v>553.6091</v>
       </c>
       <c r="G6" t="n">
-        <v>91679642.09999999</v>
+        <v>45894198</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>탑코미디어</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>134580</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3750</v>
+        <v>125800</v>
       </c>
       <c r="F7" t="n">
-        <v>12771</v>
+        <v>728.773</v>
       </c>
       <c r="G7" t="n">
-        <v>47891250</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-7.06</v>
-      </c>
+        <v>91679642.09999999</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -676,44 +674,46 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>탑코미디어</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>134580</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>72000</v>
+        <v>3750</v>
       </c>
       <c r="F8" t="n">
-        <v>665.1562</v>
+        <v>12771</v>
       </c>
       <c r="G8" t="n">
         <v>47891250</v>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>-7.06</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -722,13 +722,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>248500</v>
+        <v>72000</v>
       </c>
       <c r="F9" t="n">
-        <v>604</v>
+        <v>665.1562</v>
       </c>
       <c r="G9" t="n">
-        <v>150094000</v>
+        <v>47891250</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -740,12 +740,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -754,13 +754,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>147200</v>
+        <v>248500</v>
       </c>
       <c r="F10" t="n">
-        <v>672</v>
+        <v>604</v>
       </c>
       <c r="G10" t="n">
-        <v>98918400</v>
+        <v>150094000</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -772,12 +772,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>롯데쇼핑</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>023530</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>115300</v>
+        <v>147200</v>
       </c>
       <c r="F11" t="n">
-        <v>867</v>
+        <v>672</v>
       </c>
       <c r="G11" t="n">
-        <v>99965100</v>
+        <v>98918400</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -804,12 +804,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SFA반도체</t>
+          <t>롯데쇼핑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>036540</t>
+          <t>023530</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -818,13 +818,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>8590</v>
+        <v>115300</v>
       </c>
       <c r="F12" t="n">
-        <v>11579</v>
+        <v>867</v>
       </c>
       <c r="G12" t="n">
-        <v>99463610</v>
+        <v>99965100</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -836,12 +836,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>인바디</t>
+          <t>SFA반도체</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>041830</t>
+          <t>036540</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -850,13 +850,13 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>58700</v>
+        <v>8590</v>
       </c>
       <c r="F13" t="n">
-        <v>1715</v>
+        <v>11579</v>
       </c>
       <c r="G13" t="n">
-        <v>100670500</v>
+        <v>99463610</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>인바디</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>089970</t>
+          <t>041830</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -882,13 +882,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>49000</v>
+        <v>58700</v>
       </c>
       <c r="F14" t="n">
-        <v>2045</v>
+        <v>1715</v>
       </c>
       <c r="G14" t="n">
-        <v>100205000</v>
+        <v>100670500</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>089970</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -914,13 +914,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>14600</v>
+        <v>49000</v>
       </c>
       <c r="F15" t="n">
-        <v>6766</v>
+        <v>2045</v>
       </c>
       <c r="G15" t="n">
-        <v>98783600</v>
+        <v>100205000</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>탑코미디어</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>134580</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -946,13 +946,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4035</v>
+        <v>14600</v>
       </c>
       <c r="F16" t="n">
-        <v>12771</v>
+        <v>6766</v>
       </c>
       <c r="G16" t="n">
-        <v>51530985</v>
+        <v>98783600</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -964,12 +964,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>탑코미디어</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>420770</t>
+          <t>134580</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>99100</v>
+        <v>4035</v>
       </c>
       <c r="F17" t="n">
-        <v>1013</v>
+        <v>12771</v>
       </c>
       <c r="G17" t="n">
-        <v>100388300</v>
+        <v>51530985</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -996,29 +996,61 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>기가비스</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>420770</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>99100</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1013</v>
+      </c>
+      <c r="G18" t="n">
+        <v>100388300</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>달바글로벌</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>483650</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
         <v>163100</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F19" t="n">
         <v>613</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G19" t="n">
         <v>99980300</v>
       </c>
-      <c r="H18" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/my_mp_history.xlsx
+++ b/docs/downloads/my_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,7 +473,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,66 +488,68 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>14130</v>
+        <v>14390</v>
       </c>
       <c r="F2" t="n">
-        <v>3247.997</v>
+        <v>3192.997</v>
       </c>
       <c r="G2" t="n">
-        <v>45894198</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
+        <v>45947227.2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.84</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>메쥬</t>
+          <t>엠케이전자</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0088M0</t>
+          <t>033160</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>14130</v>
+        <v>20000</v>
       </c>
       <c r="F3" t="n">
-        <v>55</v>
+        <v>5705.9581</v>
       </c>
       <c r="G3" t="n">
-        <v>777150</v>
+        <v>114119161</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>롯데쇼핑</t>
+          <t>인바디</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>023530</t>
+          <t>041830</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -556,32 +558,32 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102200</v>
+        <v>52100</v>
       </c>
       <c r="F4" t="n">
-        <v>867</v>
+        <v>1715</v>
       </c>
       <c r="G4" t="n">
-        <v>88607400</v>
+        <v>89351500</v>
       </c>
       <c r="H4" t="n">
-        <v>-11.36</v>
+        <v>-11.24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>089970</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -590,64 +592,64 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>13980</v>
+        <v>67400</v>
       </c>
       <c r="F5" t="n">
-        <v>6766</v>
+        <v>2045</v>
       </c>
       <c r="G5" t="n">
-        <v>94588680</v>
+        <v>137833000</v>
       </c>
       <c r="H5" t="n">
-        <v>-4.25</v>
+        <v>37.55</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>82900</v>
+        <v>54000</v>
       </c>
       <c r="F6" t="n">
-        <v>553.6091</v>
+        <v>1056.6589</v>
       </c>
       <c r="G6" t="n">
-        <v>45894198</v>
+        <v>57059580.5</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>에이치브이엠</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>295310</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -656,192 +658,194 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>125800</v>
+        <v>69700</v>
       </c>
       <c r="F7" t="n">
-        <v>728.773</v>
+        <v>1637.2907</v>
       </c>
       <c r="G7" t="n">
-        <v>91679642.09999999</v>
+        <v>114119161</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>탑코미디어</t>
+          <t>메쥬</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>134580</t>
+          <t>0088M0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3750</v>
+        <v>14130</v>
       </c>
       <c r="F8" t="n">
-        <v>12771</v>
+        <v>3247.997</v>
       </c>
       <c r="G8" t="n">
-        <v>47891250</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-7.06</v>
-      </c>
+        <v>45894198</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>메쥬</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>0088M0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>72000</v>
+        <v>14130</v>
       </c>
       <c r="F9" t="n">
-        <v>665.1562</v>
+        <v>55</v>
       </c>
       <c r="G9" t="n">
-        <v>47891250</v>
+        <v>777150</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>롯데쇼핑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>023530</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>248500</v>
+        <v>102200</v>
       </c>
       <c r="F10" t="n">
-        <v>604</v>
+        <v>867</v>
       </c>
       <c r="G10" t="n">
-        <v>150094000</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
+        <v>88607400</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-11.36</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>147200</v>
+        <v>13980</v>
       </c>
       <c r="F11" t="n">
-        <v>672</v>
+        <v>6766</v>
       </c>
       <c r="G11" t="n">
-        <v>98918400</v>
-      </c>
-      <c r="H11" t="inlineStr"/>
+        <v>94588680</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-4.25</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>롯데쇼핑</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>023530</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>115300</v>
+        <v>82900</v>
       </c>
       <c r="F12" t="n">
-        <v>867</v>
+        <v>553.6091</v>
       </c>
       <c r="G12" t="n">
-        <v>99965100</v>
+        <v>45894198</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SFA반도체</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>036540</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -850,62 +854,64 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>8590</v>
+        <v>125800</v>
       </c>
       <c r="F13" t="n">
-        <v>11579</v>
+        <v>728.773</v>
       </c>
       <c r="G13" t="n">
-        <v>99463610</v>
+        <v>91679642.09999999</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>인바디</t>
+          <t>탑코미디어</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>041830</t>
+          <t>134580</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>58700</v>
+        <v>3750</v>
       </c>
       <c r="F14" t="n">
-        <v>1715</v>
+        <v>12771</v>
       </c>
       <c r="G14" t="n">
-        <v>100670500</v>
-      </c>
-      <c r="H14" t="inlineStr"/>
+        <v>47891250</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-7.06</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>089970</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -914,13 +920,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>49000</v>
+        <v>72000</v>
       </c>
       <c r="F15" t="n">
-        <v>2045</v>
+        <v>665.1562</v>
       </c>
       <c r="G15" t="n">
-        <v>100205000</v>
+        <v>47891250</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -932,12 +938,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -946,13 +952,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>14600</v>
+        <v>248500</v>
       </c>
       <c r="F16" t="n">
-        <v>6766</v>
+        <v>604</v>
       </c>
       <c r="G16" t="n">
-        <v>98783600</v>
+        <v>150094000</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -964,12 +970,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>탑코미디어</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>134580</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -978,13 +984,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4035</v>
+        <v>147200</v>
       </c>
       <c r="F17" t="n">
-        <v>12771</v>
+        <v>672</v>
       </c>
       <c r="G17" t="n">
-        <v>51530985</v>
+        <v>98918400</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -996,12 +1002,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>롯데쇼핑</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>420770</t>
+          <t>023530</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1010,13 +1016,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>99100</v>
+        <v>115300</v>
       </c>
       <c r="F18" t="n">
-        <v>1013</v>
+        <v>867</v>
       </c>
       <c r="G18" t="n">
-        <v>100388300</v>
+        <v>99965100</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1028,29 +1034,221 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>SFA반도체</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>036540</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>8590</v>
+      </c>
+      <c r="F19" t="n">
+        <v>11579</v>
+      </c>
+      <c r="G19" t="n">
+        <v>99463610</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>인바디</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>041830</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>58700</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1715</v>
+      </c>
+      <c r="G20" t="n">
+        <v>100670500</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>브이엠</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>089970</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>49000</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2045</v>
+      </c>
+      <c r="G21" t="n">
+        <v>100205000</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>후성</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>093370</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>14600</v>
+      </c>
+      <c r="F22" t="n">
+        <v>6766</v>
+      </c>
+      <c r="G22" t="n">
+        <v>98783600</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>탑코미디어</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>134580</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>4035</v>
+      </c>
+      <c r="F23" t="n">
+        <v>12771</v>
+      </c>
+      <c r="G23" t="n">
+        <v>51530985</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>기가비스</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>420770</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>99100</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1013</v>
+      </c>
+      <c r="G24" t="n">
+        <v>100388300</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>달바글로벌</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>483650</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
         <v>163100</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F25" t="n">
         <v>613</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G25" t="n">
         <v>99980300</v>
       </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/my_mp_history.xlsx
+++ b/docs/downloads/my_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,31 +478,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>메쥬</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0088M0</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>14390</v>
+        <v>276000</v>
       </c>
       <c r="F2" t="n">
-        <v>3192.997</v>
+        <v>16.2128</v>
       </c>
       <c r="G2" t="n">
-        <v>45947227.2</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.84</v>
-      </c>
+        <v>4474741.5</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -512,29 +510,31 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>엠케이전자</t>
+          <t>메쥬</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>033160</t>
+          <t>0088M0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>20000</v>
+        <v>14390</v>
       </c>
       <c r="F3" t="n">
-        <v>5705.9581</v>
+        <v>3192.997</v>
       </c>
       <c r="G3" t="n">
-        <v>114119161</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>45947227.2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.84</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -544,31 +544,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>인바디</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>041830</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>52100</v>
+        <v>164900</v>
       </c>
       <c r="F4" t="n">
-        <v>1715</v>
+        <v>20.0507</v>
       </c>
       <c r="G4" t="n">
-        <v>89351500</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-11.24</v>
-      </c>
+        <v>3306361</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -578,31 +576,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>엠케이전자</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>089970</t>
+          <t>033160</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>67400</v>
+        <v>20000</v>
       </c>
       <c r="F5" t="n">
-        <v>2045</v>
+        <v>5705.9581</v>
       </c>
       <c r="G5" t="n">
-        <v>137833000</v>
-      </c>
-      <c r="H5" t="n">
-        <v>37.55</v>
-      </c>
+        <v>114119161</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -612,27 +608,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>SFA반도체</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>036540</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>54000</v>
+        <v>11460</v>
       </c>
       <c r="F6" t="n">
-        <v>1056.6589</v>
+        <v>1620.958</v>
       </c>
       <c r="G6" t="n">
-        <v>57059580.5</v>
+        <v>18576179</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -644,176 +640,176 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>에이치브이엠</t>
+          <t>인바디</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>295310</t>
+          <t>041830</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>69700</v>
+        <v>52100</v>
       </c>
       <c r="F7" t="n">
-        <v>1637.2907</v>
+        <v>1715</v>
       </c>
       <c r="G7" t="n">
-        <v>114119161</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
+        <v>89351500</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-11.24</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>메쥬</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0088M0</t>
+          <t>089970</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>14130</v>
+        <v>67400</v>
       </c>
       <c r="F8" t="n">
-        <v>3247.997</v>
+        <v>2045</v>
       </c>
       <c r="G8" t="n">
-        <v>45894198</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
+        <v>137833000</v>
+      </c>
+      <c r="H8" t="n">
+        <v>37.55</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>메쥬</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0088M0</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>14130</v>
+        <v>92300</v>
       </c>
       <c r="F9" t="n">
-        <v>55</v>
+        <v>17.6286</v>
       </c>
       <c r="G9" t="n">
-        <v>777150</v>
+        <v>1627115.2</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>롯데쇼핑</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>023530</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102200</v>
+        <v>54000</v>
       </c>
       <c r="F10" t="n">
-        <v>867</v>
+        <v>1056.6589</v>
       </c>
       <c r="G10" t="n">
-        <v>88607400</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-11.36</v>
-      </c>
+        <v>57059580.5</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>에이치브이엠</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>295310</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>13980</v>
+        <v>69700</v>
       </c>
       <c r="F11" t="n">
-        <v>6766</v>
+        <v>1637.2907</v>
       </c>
       <c r="G11" t="n">
-        <v>94588680</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-4.25</v>
-      </c>
+        <v>114119161</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -822,96 +818,94 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>82900</v>
+        <v>139200</v>
       </c>
       <c r="F12" t="n">
-        <v>553.6091</v>
+        <v>91.04859999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>45894198</v>
+        <v>12673960.8</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>420770</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>125800</v>
+        <v>129300</v>
       </c>
       <c r="F13" t="n">
-        <v>728.773</v>
+        <v>130.4079</v>
       </c>
       <c r="G13" t="n">
-        <v>91679642.09999999</v>
+        <v>16861739</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>탑코미디어</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>134580</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3750</v>
+        <v>183400</v>
       </c>
       <c r="F14" t="n">
-        <v>12771</v>
+        <v>9.241899999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>47891250</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-7.06</v>
-      </c>
+        <v>1694961</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>메쥬</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>0088M0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -920,158 +914,162 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>72000</v>
+        <v>14130</v>
       </c>
       <c r="F15" t="n">
-        <v>665.1562</v>
+        <v>3247.997</v>
       </c>
       <c r="G15" t="n">
-        <v>47891250</v>
+        <v>45894198</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>메쥬</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>0088M0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>248500</v>
+        <v>14130</v>
       </c>
       <c r="F16" t="n">
-        <v>604</v>
+        <v>55</v>
       </c>
       <c r="G16" t="n">
-        <v>150094000</v>
+        <v>777150</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>롯데쇼핑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>023530</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>147200</v>
+        <v>102200</v>
       </c>
       <c r="F17" t="n">
-        <v>672</v>
+        <v>867</v>
       </c>
       <c r="G17" t="n">
-        <v>98918400</v>
-      </c>
-      <c r="H17" t="inlineStr"/>
+        <v>88607400</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-11.36</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>롯데쇼핑</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>023530</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>115300</v>
+        <v>13980</v>
       </c>
       <c r="F18" t="n">
-        <v>867</v>
+        <v>6766</v>
       </c>
       <c r="G18" t="n">
-        <v>99965100</v>
-      </c>
-      <c r="H18" t="inlineStr"/>
+        <v>94588680</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-4.25</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SFA반도체</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>036540</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>8590</v>
+        <v>82900</v>
       </c>
       <c r="F19" t="n">
-        <v>11579</v>
+        <v>553.6091</v>
       </c>
       <c r="G19" t="n">
-        <v>99463610</v>
+        <v>45894198</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>인바디</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>041830</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1080,62 +1078,64 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>58700</v>
+        <v>125800</v>
       </c>
       <c r="F20" t="n">
-        <v>1715</v>
+        <v>728.773</v>
       </c>
       <c r="G20" t="n">
-        <v>100670500</v>
+        <v>91679642.09999999</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>탑코미디어</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>089970</t>
+          <t>134580</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>49000</v>
+        <v>3750</v>
       </c>
       <c r="F21" t="n">
-        <v>2045</v>
+        <v>12771</v>
       </c>
       <c r="G21" t="n">
-        <v>100205000</v>
-      </c>
-      <c r="H21" t="inlineStr"/>
+        <v>47891250</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-7.06</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1144,13 +1144,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>14600</v>
+        <v>72000</v>
       </c>
       <c r="F22" t="n">
-        <v>6766</v>
+        <v>665.1562</v>
       </c>
       <c r="G22" t="n">
-        <v>98783600</v>
+        <v>47891250</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>탑코미디어</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>134580</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1176,13 +1176,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4035</v>
+        <v>248500</v>
       </c>
       <c r="F23" t="n">
-        <v>12771</v>
+        <v>604</v>
       </c>
       <c r="G23" t="n">
-        <v>51530985</v>
+        <v>150094000</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>420770</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1208,13 +1208,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>99100</v>
+        <v>147200</v>
       </c>
       <c r="F24" t="n">
-        <v>1013</v>
+        <v>672</v>
       </c>
       <c r="G24" t="n">
-        <v>100388300</v>
+        <v>98918400</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1226,29 +1226,253 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>롯데쇼핑</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>023530</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>115300</v>
+      </c>
+      <c r="F25" t="n">
+        <v>867</v>
+      </c>
+      <c r="G25" t="n">
+        <v>99965100</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SFA반도체</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>036540</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>8590</v>
+      </c>
+      <c r="F26" t="n">
+        <v>11579</v>
+      </c>
+      <c r="G26" t="n">
+        <v>99463610</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>인바디</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>041830</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>58700</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1715</v>
+      </c>
+      <c r="G27" t="n">
+        <v>100670500</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>브이엠</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>089970</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>49000</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2045</v>
+      </c>
+      <c r="G28" t="n">
+        <v>100205000</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>후성</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>093370</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>14600</v>
+      </c>
+      <c r="F29" t="n">
+        <v>6766</v>
+      </c>
+      <c r="G29" t="n">
+        <v>98783600</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>탑코미디어</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>134580</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>4035</v>
+      </c>
+      <c r="F30" t="n">
+        <v>12771</v>
+      </c>
+      <c r="G30" t="n">
+        <v>51530985</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>기가비스</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>420770</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>99100</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1013</v>
+      </c>
+      <c r="G31" t="n">
+        <v>100388300</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>달바글로벌</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>483650</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
         <v>163100</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F32" t="n">
         <v>613</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G32" t="n">
         <v>99980300</v>
       </c>
-      <c r="H25" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/my_mp_history.xlsx
+++ b/docs/downloads/my_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -708,27 +708,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>윈팩</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>097800</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>92300</v>
+        <v>4025</v>
       </c>
       <c r="F9" t="n">
-        <v>17.6286</v>
+        <v>14176.2933</v>
       </c>
       <c r="G9" t="n">
-        <v>1627115.2</v>
+        <v>57059580.5</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -740,27 +740,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>54000</v>
+        <v>92300</v>
       </c>
       <c r="F10" t="n">
-        <v>1056.6589</v>
+        <v>17.6286</v>
       </c>
       <c r="G10" t="n">
-        <v>57059580.5</v>
+        <v>1627115.2</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -772,29 +772,31 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>에이치브이엠</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>295310</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>69700</v>
+        <v>92300</v>
       </c>
       <c r="F11" t="n">
-        <v>1637.2907</v>
+        <v>1236.3939</v>
       </c>
       <c r="G11" t="n">
         <v>114119161</v>
       </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="n">
+        <v>19.61</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -804,27 +806,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>139200</v>
+        <v>54000</v>
       </c>
       <c r="F12" t="n">
-        <v>91.04859999999999</v>
+        <v>1056.6589</v>
       </c>
       <c r="G12" t="n">
-        <v>12673960.8</v>
+        <v>57059580.5</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -836,27 +838,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>420770</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>129300</v>
+        <v>54000</v>
       </c>
       <c r="F13" t="n">
-        <v>130.4079</v>
+        <v>1056.6589</v>
       </c>
       <c r="G13" t="n">
-        <v>16861739</v>
+        <v>57059580.5</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -868,76 +870,76 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>에이치브이엠</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>295310</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>183400</v>
+        <v>69700</v>
       </c>
       <c r="F14" t="n">
-        <v>9.241899999999999</v>
+        <v>1637.2907</v>
       </c>
       <c r="G14" t="n">
-        <v>1694961</v>
+        <v>114119161</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>메쥬</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0088M0</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>14130</v>
+        <v>139200</v>
       </c>
       <c r="F15" t="n">
-        <v>3247.997</v>
+        <v>91.04859999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>45894198</v>
+        <v>12673960.8</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>메쥬</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0088M0</t>
+          <t>420770</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -946,49 +948,47 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>14130</v>
+        <v>129300</v>
       </c>
       <c r="F16" t="n">
-        <v>55</v>
+        <v>130.4079</v>
       </c>
       <c r="G16" t="n">
-        <v>777150</v>
+        <v>16861739</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>롯데쇼핑</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>023530</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102200</v>
+        <v>183400</v>
       </c>
       <c r="F17" t="n">
-        <v>867</v>
+        <v>9.241899999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>88607400</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-11.36</v>
-      </c>
+        <v>1694961</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -998,31 +998,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>메쥬</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>0088M0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>13980</v>
+        <v>14130</v>
       </c>
       <c r="F18" t="n">
-        <v>6766</v>
+        <v>3247.997</v>
       </c>
       <c r="G18" t="n">
-        <v>94588680</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-4.25</v>
-      </c>
+        <v>45894198</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1032,27 +1030,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>메쥬</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>0088M0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>82900</v>
+        <v>14130</v>
       </c>
       <c r="F19" t="n">
-        <v>553.6091</v>
+        <v>55</v>
       </c>
       <c r="G19" t="n">
-        <v>45894198</v>
+        <v>777150</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1064,44 +1062,46 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>롯데쇼핑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>023530</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>125800</v>
+        <v>102200</v>
       </c>
       <c r="F20" t="n">
-        <v>728.773</v>
+        <v>867</v>
       </c>
       <c r="G20" t="n">
-        <v>91679642.09999999</v>
-      </c>
-      <c r="H20" t="inlineStr"/>
+        <v>88607400</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-11.36</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>탑코미디어</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>134580</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1110,22 +1110,22 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3750</v>
+        <v>13980</v>
       </c>
       <c r="F21" t="n">
-        <v>12771</v>
+        <v>6766</v>
       </c>
       <c r="G21" t="n">
-        <v>47891250</v>
+        <v>94588680</v>
       </c>
       <c r="H21" t="n">
-        <v>-7.06</v>
+        <v>-4.25</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1140,34 +1140,34 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>72000</v>
+        <v>82900</v>
       </c>
       <c r="F22" t="n">
-        <v>665.1562</v>
+        <v>553.6091</v>
       </c>
       <c r="G22" t="n">
-        <v>47891250</v>
+        <v>45894198</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1176,62 +1176,64 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>248500</v>
+        <v>125800</v>
       </c>
       <c r="F23" t="n">
-        <v>604</v>
+        <v>728.773</v>
       </c>
       <c r="G23" t="n">
-        <v>150094000</v>
+        <v>91679642.09999999</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>탑코미디어</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>134580</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>147200</v>
+        <v>3750</v>
       </c>
       <c r="F24" t="n">
-        <v>672</v>
+        <v>12771</v>
       </c>
       <c r="G24" t="n">
-        <v>98918400</v>
-      </c>
-      <c r="H24" t="inlineStr"/>
+        <v>47891250</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-7.06</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>롯데쇼핑</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>023530</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1240,13 +1242,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>115300</v>
+        <v>72000</v>
       </c>
       <c r="F25" t="n">
-        <v>867</v>
+        <v>665.1562</v>
       </c>
       <c r="G25" t="n">
-        <v>99965100</v>
+        <v>47891250</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1258,12 +1260,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SFA반도체</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>036540</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1272,13 +1274,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>8590</v>
+        <v>248500</v>
       </c>
       <c r="F26" t="n">
-        <v>11579</v>
+        <v>604</v>
       </c>
       <c r="G26" t="n">
-        <v>99463610</v>
+        <v>150094000</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1290,12 +1292,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>인바디</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>041830</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1304,13 +1306,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>58700</v>
+        <v>147200</v>
       </c>
       <c r="F27" t="n">
-        <v>1715</v>
+        <v>672</v>
       </c>
       <c r="G27" t="n">
-        <v>100670500</v>
+        <v>98918400</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1322,12 +1324,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>롯데쇼핑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>089970</t>
+          <t>023530</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1336,13 +1338,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>49000</v>
+        <v>115300</v>
       </c>
       <c r="F28" t="n">
-        <v>2045</v>
+        <v>867</v>
       </c>
       <c r="G28" t="n">
-        <v>100205000</v>
+        <v>99965100</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1354,12 +1356,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>SFA반도체</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>036540</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1368,13 +1370,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>14600</v>
+        <v>8590</v>
       </c>
       <c r="F29" t="n">
-        <v>6766</v>
+        <v>11579</v>
       </c>
       <c r="G29" t="n">
-        <v>98783600</v>
+        <v>99463610</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1386,12 +1388,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>탑코미디어</t>
+          <t>인바디</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>134580</t>
+          <t>041830</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1400,13 +1402,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4035</v>
+        <v>58700</v>
       </c>
       <c r="F30" t="n">
-        <v>12771</v>
+        <v>1715</v>
       </c>
       <c r="G30" t="n">
-        <v>51530985</v>
+        <v>100670500</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1418,12 +1420,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>420770</t>
+          <t>089970</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1432,13 +1434,13 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>99100</v>
+        <v>49000</v>
       </c>
       <c r="F31" t="n">
-        <v>1013</v>
+        <v>2045</v>
       </c>
       <c r="G31" t="n">
-        <v>100388300</v>
+        <v>100205000</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1450,29 +1452,125 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>후성</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>093370</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>14600</v>
+      </c>
+      <c r="F32" t="n">
+        <v>6766</v>
+      </c>
+      <c r="G32" t="n">
+        <v>98783600</v>
+      </c>
+      <c r="H32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>탑코미디어</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>134580</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>4035</v>
+      </c>
+      <c r="F33" t="n">
+        <v>12771</v>
+      </c>
+      <c r="G33" t="n">
+        <v>51530985</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>기가비스</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>420770</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>99100</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1013</v>
+      </c>
+      <c r="G34" t="n">
+        <v>100388300</v>
+      </c>
+      <c r="H34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
           <t>달바글로벌</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>483650</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
         <v>163100</v>
       </c>
-      <c r="F32" t="n">
+      <c r="F35" t="n">
         <v>613</v>
       </c>
-      <c r="G32" t="n">
+      <c r="G35" t="n">
         <v>99980300</v>
       </c>
-      <c r="H32" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/my_mp_history.xlsx
+++ b/docs/downloads/my_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,49 +473,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>276000</v>
+        <v>15190</v>
       </c>
       <c r="F2" t="n">
-        <v>16.2128</v>
+        <v>6935.1909</v>
       </c>
       <c r="G2" t="n">
-        <v>4474741.5</v>
+        <v>105345550.5</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>메쥬</t>
+          <t>윈팩</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0088M0</t>
+          <t>097800</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -524,81 +524,83 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>14390</v>
+        <v>3280</v>
       </c>
       <c r="F3" t="n">
-        <v>3192.997</v>
+        <v>14176.2933</v>
       </c>
       <c r="G3" t="n">
-        <v>45947227.2</v>
+        <v>46498242</v>
       </c>
       <c r="H3" t="n">
-        <v>1.84</v>
+        <v>-18.51</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>나노신소재</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>121600</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>164900</v>
+        <v>60400</v>
       </c>
       <c r="F4" t="n">
-        <v>20.0507</v>
+        <v>769.8384</v>
       </c>
       <c r="G4" t="n">
-        <v>3306361</v>
+        <v>46498242</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>엠케이전자</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>033160</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>20000</v>
+        <v>169300</v>
       </c>
       <c r="F5" t="n">
-        <v>5705.9581</v>
+        <v>622.2419</v>
       </c>
       <c r="G5" t="n">
-        <v>114119161</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>105345550.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.61</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -608,27 +610,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SFA반도체</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>036540</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>11460</v>
+        <v>276000</v>
       </c>
       <c r="F6" t="n">
-        <v>1620.958</v>
+        <v>16.2128</v>
       </c>
       <c r="G6" t="n">
-        <v>18576179</v>
+        <v>4474741.5</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -640,12 +642,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>인바디</t>
+          <t>메쥬</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>041830</t>
+          <t>0088M0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -654,16 +656,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>52100</v>
+        <v>14390</v>
       </c>
       <c r="F7" t="n">
-        <v>1715</v>
+        <v>3192.997</v>
       </c>
       <c r="G7" t="n">
-        <v>89351500</v>
+        <v>45947227.2</v>
       </c>
       <c r="H7" t="n">
-        <v>-11.24</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="8">
@@ -674,31 +676,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>089970</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>67400</v>
+        <v>164900</v>
       </c>
       <c r="F8" t="n">
-        <v>2045</v>
+        <v>20.0507</v>
       </c>
       <c r="G8" t="n">
-        <v>137833000</v>
-      </c>
-      <c r="H8" t="n">
-        <v>37.55</v>
-      </c>
+        <v>3306361</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>윈팩</t>
+          <t>엠케이전자</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>097800</t>
+          <t>033160</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -722,13 +722,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4025</v>
+        <v>20000</v>
       </c>
       <c r="F9" t="n">
-        <v>14176.2933</v>
+        <v>5705.9581</v>
       </c>
       <c r="G9" t="n">
-        <v>57059580.5</v>
+        <v>114119161</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -740,27 +740,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>SFA반도체</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>036540</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>92300</v>
+        <v>11460</v>
       </c>
       <c r="F10" t="n">
-        <v>17.6286</v>
+        <v>1620.958</v>
       </c>
       <c r="G10" t="n">
-        <v>1627115.2</v>
+        <v>18576179</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -772,12 +772,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>인바디</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>041830</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -786,16 +786,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>92300</v>
+        <v>52100</v>
       </c>
       <c r="F11" t="n">
-        <v>1236.3939</v>
+        <v>1715</v>
       </c>
       <c r="G11" t="n">
-        <v>114119161</v>
+        <v>89351500</v>
       </c>
       <c r="H11" t="n">
-        <v>19.61</v>
+        <v>-11.24</v>
       </c>
     </row>
     <row r="12">
@@ -806,29 +806,31 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>089970</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>54000</v>
+        <v>67400</v>
       </c>
       <c r="F12" t="n">
-        <v>1056.6589</v>
+        <v>2045</v>
       </c>
       <c r="G12" t="n">
-        <v>57059580.5</v>
-      </c>
-      <c r="H12" t="inlineStr"/>
+        <v>137833000</v>
+      </c>
+      <c r="H12" t="n">
+        <v>37.55</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -838,24 +840,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>윈팩</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>097800</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>54000</v>
+        <v>4025</v>
       </c>
       <c r="F13" t="n">
-        <v>1056.6589</v>
+        <v>14176.2933</v>
       </c>
       <c r="G13" t="n">
         <v>57059580.5</v>
@@ -870,27 +872,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>에이치브이엠</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>295310</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>69700</v>
+        <v>92300</v>
       </c>
       <c r="F14" t="n">
-        <v>1637.2907</v>
+        <v>17.6286</v>
       </c>
       <c r="G14" t="n">
-        <v>114119161</v>
+        <v>1627115.2</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -902,29 +904,31 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>139200</v>
+        <v>92300</v>
       </c>
       <c r="F15" t="n">
-        <v>91.04859999999999</v>
+        <v>1236.3939</v>
       </c>
       <c r="G15" t="n">
-        <v>12673960.8</v>
-      </c>
-      <c r="H15" t="inlineStr"/>
+        <v>114119161</v>
+      </c>
+      <c r="H15" t="n">
+        <v>19.61</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -934,27 +938,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>420770</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>129300</v>
+        <v>54000</v>
       </c>
       <c r="F16" t="n">
-        <v>130.4079</v>
+        <v>1056.6589</v>
       </c>
       <c r="G16" t="n">
-        <v>16861739</v>
+        <v>57059580.5</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -966,12 +970,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -980,30 +984,30 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>183400</v>
+        <v>54000</v>
       </c>
       <c r="F17" t="n">
-        <v>9.241899999999999</v>
+        <v>1056.6589</v>
       </c>
       <c r="G17" t="n">
-        <v>1694961</v>
+        <v>57059580.5</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>메쥬</t>
+          <t>에이치브이엠</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0088M0</t>
+          <t>295310</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1012,115 +1016,111 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>14130</v>
+        <v>69700</v>
       </c>
       <c r="F18" t="n">
-        <v>3247.997</v>
+        <v>1637.2907</v>
       </c>
       <c r="G18" t="n">
-        <v>45894198</v>
+        <v>114119161</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>메쥬</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0088M0</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>14130</v>
+        <v>139200</v>
       </c>
       <c r="F19" t="n">
-        <v>55</v>
+        <v>91.04859999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>777150</v>
+        <v>12673960.8</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>롯데쇼핑</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>023530</t>
+          <t>420770</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102200</v>
+        <v>129300</v>
       </c>
       <c r="F20" t="n">
-        <v>867</v>
+        <v>130.4079</v>
       </c>
       <c r="G20" t="n">
-        <v>88607400</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-11.36</v>
-      </c>
+        <v>16861739</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>13980</v>
+        <v>183400</v>
       </c>
       <c r="F21" t="n">
-        <v>6766</v>
+        <v>9.241899999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>94588680</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-4.25</v>
-      </c>
+        <v>1694961</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1130,24 +1130,24 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>메쥬</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>0088M0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>82900</v>
+        <v>14130</v>
       </c>
       <c r="F22" t="n">
-        <v>553.6091</v>
+        <v>3247.997</v>
       </c>
       <c r="G22" t="n">
         <v>45894198</v>
@@ -1162,44 +1162,44 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>메쥬</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>0088M0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>125800</v>
+        <v>14130</v>
       </c>
       <c r="F23" t="n">
-        <v>728.773</v>
+        <v>55</v>
       </c>
       <c r="G23" t="n">
-        <v>91679642.09999999</v>
+        <v>777150</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>탑코미디어</t>
+          <t>롯데쇼핑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>134580</t>
+          <t>023530</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1208,96 +1208,98 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3750</v>
+        <v>102200</v>
       </c>
       <c r="F24" t="n">
-        <v>12771</v>
+        <v>867</v>
       </c>
       <c r="G24" t="n">
-        <v>47891250</v>
+        <v>88607400</v>
       </c>
       <c r="H24" t="n">
-        <v>-7.06</v>
+        <v>-11.36</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>72000</v>
+        <v>13980</v>
       </c>
       <c r="F25" t="n">
-        <v>665.1562</v>
+        <v>6766</v>
       </c>
       <c r="G25" t="n">
-        <v>47891250</v>
-      </c>
-      <c r="H25" t="inlineStr"/>
+        <v>94588680</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-4.25</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>248500</v>
+        <v>82900</v>
       </c>
       <c r="F26" t="n">
-        <v>604</v>
+        <v>553.6091</v>
       </c>
       <c r="G26" t="n">
-        <v>150094000</v>
+        <v>45894198</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1306,62 +1308,64 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>147200</v>
+        <v>125800</v>
       </c>
       <c r="F27" t="n">
-        <v>672</v>
+        <v>728.773</v>
       </c>
       <c r="G27" t="n">
-        <v>98918400</v>
+        <v>91679642.09999999</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>롯데쇼핑</t>
+          <t>탑코미디어</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>023530</t>
+          <t>134580</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>115300</v>
+        <v>3750</v>
       </c>
       <c r="F28" t="n">
-        <v>867</v>
+        <v>12771</v>
       </c>
       <c r="G28" t="n">
-        <v>99965100</v>
-      </c>
-      <c r="H28" t="inlineStr"/>
+        <v>47891250</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-7.06</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SFA반도체</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>036540</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1370,13 +1374,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>8590</v>
+        <v>72000</v>
       </c>
       <c r="F29" t="n">
-        <v>11579</v>
+        <v>665.1562</v>
       </c>
       <c r="G29" t="n">
-        <v>99463610</v>
+        <v>47891250</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1388,12 +1392,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>인바디</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>041830</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1402,13 +1406,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>58700</v>
+        <v>248500</v>
       </c>
       <c r="F30" t="n">
-        <v>1715</v>
+        <v>604</v>
       </c>
       <c r="G30" t="n">
-        <v>100670500</v>
+        <v>150094000</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1420,12 +1424,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>089970</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1434,13 +1438,13 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>49000</v>
+        <v>147200</v>
       </c>
       <c r="F31" t="n">
-        <v>2045</v>
+        <v>672</v>
       </c>
       <c r="G31" t="n">
-        <v>100205000</v>
+        <v>98918400</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1452,12 +1456,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>롯데쇼핑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>023530</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1466,13 +1470,13 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>14600</v>
+        <v>115300</v>
       </c>
       <c r="F32" t="n">
-        <v>6766</v>
+        <v>867</v>
       </c>
       <c r="G32" t="n">
-        <v>98783600</v>
+        <v>99965100</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1484,12 +1488,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>탑코미디어</t>
+          <t>SFA반도체</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>134580</t>
+          <t>036540</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1498,13 +1502,13 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4035</v>
+        <v>8590</v>
       </c>
       <c r="F33" t="n">
-        <v>12771</v>
+        <v>11579</v>
       </c>
       <c r="G33" t="n">
-        <v>51530985</v>
+        <v>99463610</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1516,12 +1520,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>인바디</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>420770</t>
+          <t>041830</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1530,13 +1534,13 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>99100</v>
+        <v>58700</v>
       </c>
       <c r="F34" t="n">
-        <v>1013</v>
+        <v>1715</v>
       </c>
       <c r="G34" t="n">
-        <v>100388300</v>
+        <v>100670500</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1548,29 +1552,157 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>브이엠</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>089970</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>49000</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2045</v>
+      </c>
+      <c r="G35" t="n">
+        <v>100205000</v>
+      </c>
+      <c r="H35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>후성</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>093370</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>14600</v>
+      </c>
+      <c r="F36" t="n">
+        <v>6766</v>
+      </c>
+      <c r="G36" t="n">
+        <v>98783600</v>
+      </c>
+      <c r="H36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>탑코미디어</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>134580</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>4035</v>
+      </c>
+      <c r="F37" t="n">
+        <v>12771</v>
+      </c>
+      <c r="G37" t="n">
+        <v>51530985</v>
+      </c>
+      <c r="H37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>기가비스</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>420770</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>99100</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1013</v>
+      </c>
+      <c r="G38" t="n">
+        <v>100388300</v>
+      </c>
+      <c r="H38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
           <t>달바글로벌</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>483650</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
         <v>163100</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F39" t="n">
         <v>613</v>
       </c>
-      <c r="G35" t="n">
+      <c r="G39" t="n">
         <v>99980300</v>
       </c>
-      <c r="H35" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/my_mp_history.xlsx
+++ b/docs/downloads/my_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,49 +473,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>엠케이전자</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>033160</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>15190</v>
+        <v>17050</v>
       </c>
       <c r="F2" t="n">
-        <v>6935.1909</v>
+        <v>5705.9581</v>
       </c>
       <c r="G2" t="n">
-        <v>105345550.5</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
+        <v>97286584.8</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-14.75</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>윈팩</t>
+          <t>SFA반도체</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>097800</t>
+          <t>036540</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -524,22 +526,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3280</v>
+        <v>9320</v>
       </c>
       <c r="F3" t="n">
-        <v>14176.2933</v>
+        <v>9958.041999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>46498242</v>
+        <v>92808951.2</v>
       </c>
       <c r="H3" t="n">
-        <v>-18.51</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -554,230 +556,230 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>60400</v>
+        <v>57200</v>
       </c>
       <c r="F4" t="n">
         <v>769.8384</v>
       </c>
       <c r="G4" t="n">
-        <v>46498242</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+        <v>44034759</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-5.3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>예스티</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>122640</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>169300</v>
+        <v>26600</v>
       </c>
       <c r="F5" t="n">
-        <v>622.2419</v>
+        <v>3657.3904</v>
       </c>
       <c r="G5" t="n">
-        <v>105345550.5</v>
-      </c>
-      <c r="H5" t="n">
-        <v>3.61</v>
-      </c>
+        <v>97286584.8</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>에이팩트</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>200470</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>276000</v>
+        <v>9320</v>
       </c>
       <c r="F6" t="n">
-        <v>16.2128</v>
+        <v>4724.7595</v>
       </c>
       <c r="G6" t="n">
-        <v>4474741.5</v>
+        <v>44034759</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>메쥬</t>
+          <t>하이브</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0088M0</t>
+          <t>352820</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>14390</v>
+        <v>177500</v>
       </c>
       <c r="F7" t="n">
-        <v>3192.997</v>
+        <v>522.8673</v>
       </c>
       <c r="G7" t="n">
-        <v>45947227.2</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.84</v>
-      </c>
+        <v>92808951.2</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>164900</v>
+        <v>15190</v>
       </c>
       <c r="F8" t="n">
-        <v>20.0507</v>
+        <v>6935.1909</v>
       </c>
       <c r="G8" t="n">
-        <v>3306361</v>
+        <v>105345550.5</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>엠케이전자</t>
+          <t>윈팩</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>033160</t>
+          <t>097800</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>20000</v>
+        <v>3280</v>
       </c>
       <c r="F9" t="n">
-        <v>5705.9581</v>
+        <v>14176.2933</v>
       </c>
       <c r="G9" t="n">
-        <v>114119161</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
+        <v>46498242</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-18.51</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SFA반도체</t>
+          <t>나노신소재</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>036540</t>
+          <t>121600</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>11460</v>
+        <v>60400</v>
       </c>
       <c r="F10" t="n">
-        <v>1620.958</v>
+        <v>769.8384</v>
       </c>
       <c r="G10" t="n">
-        <v>18576179</v>
+        <v>46498242</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>인바디</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>041830</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -786,16 +788,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>52100</v>
+        <v>169300</v>
       </c>
       <c r="F11" t="n">
-        <v>1715</v>
+        <v>622.2419</v>
       </c>
       <c r="G11" t="n">
-        <v>89351500</v>
+        <v>105345550.5</v>
       </c>
       <c r="H11" t="n">
-        <v>-11.24</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="12">
@@ -806,31 +808,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>089970</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>67400</v>
+        <v>276000</v>
       </c>
       <c r="F12" t="n">
-        <v>2045</v>
+        <v>16.2128</v>
       </c>
       <c r="G12" t="n">
-        <v>137833000</v>
-      </c>
-      <c r="H12" t="n">
-        <v>37.55</v>
-      </c>
+        <v>4474741.5</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -840,29 +840,31 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>윈팩</t>
+          <t>메쥬</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>097800</t>
+          <t>0088M0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4025</v>
+        <v>14390</v>
       </c>
       <c r="F13" t="n">
-        <v>14176.2933</v>
+        <v>3192.997</v>
       </c>
       <c r="G13" t="n">
-        <v>57059580.5</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
+        <v>45947227.2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.84</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -872,12 +874,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -886,13 +888,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>92300</v>
+        <v>164900</v>
       </c>
       <c r="F14" t="n">
-        <v>17.6286</v>
+        <v>20.0507</v>
       </c>
       <c r="G14" t="n">
-        <v>1627115.2</v>
+        <v>3306361</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -904,31 +906,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>엠케이전자</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>033160</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>92300</v>
+        <v>20000</v>
       </c>
       <c r="F15" t="n">
-        <v>1236.3939</v>
+        <v>5705.9581</v>
       </c>
       <c r="G15" t="n">
         <v>114119161</v>
       </c>
-      <c r="H15" t="n">
-        <v>19.61</v>
-      </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -938,27 +938,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>SFA반도체</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>036540</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>54000</v>
+        <v>11460</v>
       </c>
       <c r="F16" t="n">
-        <v>1056.6589</v>
+        <v>1620.958</v>
       </c>
       <c r="G16" t="n">
-        <v>57059580.5</v>
+        <v>18576179</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -970,29 +970,31 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>인바디</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>041830</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>54000</v>
+        <v>52100</v>
       </c>
       <c r="F17" t="n">
-        <v>1056.6589</v>
+        <v>1715</v>
       </c>
       <c r="G17" t="n">
-        <v>57059580.5</v>
-      </c>
-      <c r="H17" t="inlineStr"/>
+        <v>89351500</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-11.24</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1002,29 +1004,31 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>에이치브이엠</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>295310</t>
+          <t>089970</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>69700</v>
+        <v>67400</v>
       </c>
       <c r="F18" t="n">
-        <v>1637.2907</v>
+        <v>2045</v>
       </c>
       <c r="G18" t="n">
-        <v>114119161</v>
-      </c>
-      <c r="H18" t="inlineStr"/>
+        <v>137833000</v>
+      </c>
+      <c r="H18" t="n">
+        <v>37.55</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1034,27 +1038,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>윈팩</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>097800</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>139200</v>
+        <v>4025</v>
       </c>
       <c r="F19" t="n">
-        <v>91.04859999999999</v>
+        <v>14176.2933</v>
       </c>
       <c r="G19" t="n">
-        <v>12673960.8</v>
+        <v>57059580.5</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1066,27 +1070,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>420770</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>129300</v>
+        <v>92300</v>
       </c>
       <c r="F20" t="n">
-        <v>130.4079</v>
+        <v>17.6286</v>
       </c>
       <c r="G20" t="n">
-        <v>16861739</v>
+        <v>1627115.2</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1098,44 +1102,46 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>183400</v>
+        <v>92300</v>
       </c>
       <c r="F21" t="n">
-        <v>9.241899999999999</v>
+        <v>1236.3939</v>
       </c>
       <c r="G21" t="n">
-        <v>1694961</v>
-      </c>
-      <c r="H21" t="inlineStr"/>
+        <v>114119161</v>
+      </c>
+      <c r="H21" t="n">
+        <v>19.61</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>메쥬</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0088M0</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1144,356 +1150,354 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>14130</v>
+        <v>54000</v>
       </c>
       <c r="F22" t="n">
-        <v>3247.997</v>
+        <v>1056.6589</v>
       </c>
       <c r="G22" t="n">
-        <v>45894198</v>
+        <v>57059580.5</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>메쥬</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0088M0</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>14130</v>
+        <v>54000</v>
       </c>
       <c r="F23" t="n">
-        <v>55</v>
+        <v>1056.6589</v>
       </c>
       <c r="G23" t="n">
-        <v>777150</v>
+        <v>57059580.5</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>롯데쇼핑</t>
+          <t>에이치브이엠</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>023530</t>
+          <t>295310</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102200</v>
+        <v>69700</v>
       </c>
       <c r="F24" t="n">
-        <v>867</v>
+        <v>1637.2907</v>
       </c>
       <c r="G24" t="n">
-        <v>88607400</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-11.36</v>
-      </c>
+        <v>114119161</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>13980</v>
+        <v>139200</v>
       </c>
       <c r="F25" t="n">
-        <v>6766</v>
+        <v>91.04859999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>94588680</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-4.25</v>
-      </c>
+        <v>12673960.8</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>420770</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>82900</v>
+        <v>129300</v>
       </c>
       <c r="F26" t="n">
-        <v>553.6091</v>
+        <v>130.4079</v>
       </c>
       <c r="G26" t="n">
-        <v>45894198</v>
+        <v>16861739</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>125800</v>
+        <v>183400</v>
       </c>
       <c r="F27" t="n">
-        <v>728.773</v>
+        <v>9.241899999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>91679642.09999999</v>
+        <v>1694961</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>탑코미디어</t>
+          <t>메쥬</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>134580</t>
+          <t>0088M0</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3750</v>
+        <v>14130</v>
       </c>
       <c r="F28" t="n">
-        <v>12771</v>
+        <v>3247.997</v>
       </c>
       <c r="G28" t="n">
-        <v>47891250</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-7.06</v>
-      </c>
+        <v>45894198</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>메쥬</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>0088M0</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>72000</v>
+        <v>14130</v>
       </c>
       <c r="F29" t="n">
-        <v>665.1562</v>
+        <v>55</v>
       </c>
       <c r="G29" t="n">
-        <v>47891250</v>
+        <v>777150</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>롯데쇼핑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>023530</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>248500</v>
+        <v>102200</v>
       </c>
       <c r="F30" t="n">
-        <v>604</v>
+        <v>867</v>
       </c>
       <c r="G30" t="n">
-        <v>150094000</v>
-      </c>
-      <c r="H30" t="inlineStr"/>
+        <v>88607400</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-11.36</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>147200</v>
+        <v>13980</v>
       </c>
       <c r="F31" t="n">
-        <v>672</v>
+        <v>6766</v>
       </c>
       <c r="G31" t="n">
-        <v>98918400</v>
-      </c>
-      <c r="H31" t="inlineStr"/>
+        <v>94588680</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-4.25</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>롯데쇼핑</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>023530</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>115300</v>
+        <v>82900</v>
       </c>
       <c r="F32" t="n">
-        <v>867</v>
+        <v>553.6091</v>
       </c>
       <c r="G32" t="n">
-        <v>99965100</v>
+        <v>45894198</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SFA반도체</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>036540</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1502,62 +1506,64 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>8590</v>
+        <v>125800</v>
       </c>
       <c r="F33" t="n">
-        <v>11579</v>
+        <v>728.773</v>
       </c>
       <c r="G33" t="n">
-        <v>99463610</v>
+        <v>91679642.09999999</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>인바디</t>
+          <t>탑코미디어</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>041830</t>
+          <t>134580</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>58700</v>
+        <v>3750</v>
       </c>
       <c r="F34" t="n">
-        <v>1715</v>
+        <v>12771</v>
       </c>
       <c r="G34" t="n">
-        <v>100670500</v>
-      </c>
-      <c r="H34" t="inlineStr"/>
+        <v>47891250</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-7.06</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>089970</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1566,13 +1572,13 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>49000</v>
+        <v>72000</v>
       </c>
       <c r="F35" t="n">
-        <v>2045</v>
+        <v>665.1562</v>
       </c>
       <c r="G35" t="n">
-        <v>100205000</v>
+        <v>47891250</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1584,12 +1590,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1598,13 +1604,13 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>14600</v>
+        <v>248500</v>
       </c>
       <c r="F36" t="n">
-        <v>6766</v>
+        <v>604</v>
       </c>
       <c r="G36" t="n">
-        <v>98783600</v>
+        <v>150094000</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1616,12 +1622,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>탑코미디어</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>134580</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1630,13 +1636,13 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4035</v>
+        <v>147200</v>
       </c>
       <c r="F37" t="n">
-        <v>12771</v>
+        <v>672</v>
       </c>
       <c r="G37" t="n">
-        <v>51530985</v>
+        <v>98918400</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1648,12 +1654,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>롯데쇼핑</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>420770</t>
+          <t>023530</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1662,13 +1668,13 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>99100</v>
+        <v>115300</v>
       </c>
       <c r="F38" t="n">
-        <v>1013</v>
+        <v>867</v>
       </c>
       <c r="G38" t="n">
-        <v>100388300</v>
+        <v>99965100</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1680,29 +1686,221 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>SFA반도체</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>036540</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>8590</v>
+      </c>
+      <c r="F39" t="n">
+        <v>11579</v>
+      </c>
+      <c r="G39" t="n">
+        <v>99463610</v>
+      </c>
+      <c r="H39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>인바디</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>041830</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>58700</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1715</v>
+      </c>
+      <c r="G40" t="n">
+        <v>100670500</v>
+      </c>
+      <c r="H40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>브이엠</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>089970</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>49000</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2045</v>
+      </c>
+      <c r="G41" t="n">
+        <v>100205000</v>
+      </c>
+      <c r="H41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>후성</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>093370</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>14600</v>
+      </c>
+      <c r="F42" t="n">
+        <v>6766</v>
+      </c>
+      <c r="G42" t="n">
+        <v>98783600</v>
+      </c>
+      <c r="H42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>탑코미디어</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>134580</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>4035</v>
+      </c>
+      <c r="F43" t="n">
+        <v>12771</v>
+      </c>
+      <c r="G43" t="n">
+        <v>51530985</v>
+      </c>
+      <c r="H43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>기가비스</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>420770</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>99100</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1013</v>
+      </c>
+      <c r="G44" t="n">
+        <v>100388300</v>
+      </c>
+      <c r="H44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
           <t>달바글로벌</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>483650</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
         <v>163100</v>
       </c>
-      <c r="F39" t="n">
+      <c r="F45" t="n">
         <v>613</v>
       </c>
-      <c r="G39" t="n">
+      <c r="G45" t="n">
         <v>99980300</v>
       </c>
-      <c r="H39" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/my_mp_history.xlsx
+++ b/docs/downloads/my_mp_history.xlsx
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>54000</v>
+        <v>27134.41</v>
       </c>
       <c r="F22" t="n">
-        <v>1056.6589</v>
+        <v>2102.8495</v>
       </c>
       <c r="G22" t="n">
         <v>57059580.5</v>
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>54000</v>
+        <v>27134.41</v>
       </c>
       <c r="F23" t="n">
-        <v>1056.6589</v>
+        <v>2102.8495</v>
       </c>
       <c r="G23" t="n">
         <v>57059580.5</v>

--- a/docs/downloads/my_mp_history.xlsx
+++ b/docs/downloads/my_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,51 +473,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>엠케이전자</t>
+          <t>나노엔텍</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>033160</t>
+          <t>039860</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>17050</v>
+        <v>4865</v>
       </c>
       <c r="F2" t="n">
-        <v>5705.9581</v>
+        <v>14879.8034</v>
       </c>
       <c r="G2" t="n">
-        <v>97286584.8</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-14.75</v>
-      </c>
+        <v>72390243.59999999</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SFA반도체</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>036540</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -526,16 +524,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>9320</v>
+        <v>88300</v>
       </c>
       <c r="F3" t="n">
-        <v>9958.041999999999</v>
+        <v>819.8216</v>
       </c>
       <c r="G3" t="n">
-        <v>92808951.2</v>
+        <v>72390243.59999999</v>
       </c>
       <c r="H3" t="n">
-        <v>8.5</v>
+        <v>-30.63</v>
       </c>
     </row>
     <row r="4">
@@ -546,12 +544,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>나노신소재</t>
+          <t>엠케이전자</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>121600</t>
+          <t>033160</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -560,16 +558,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>57200</v>
+        <v>17050</v>
       </c>
       <c r="F4" t="n">
-        <v>769.8384</v>
+        <v>5705.9581</v>
       </c>
       <c r="G4" t="n">
-        <v>44034759</v>
+        <v>97286584.8</v>
       </c>
       <c r="H4" t="n">
-        <v>-5.3</v>
+        <v>-14.75</v>
       </c>
     </row>
     <row r="5">
@@ -580,29 +578,31 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>예스티</t>
+          <t>SFA반도체</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>122640</t>
+          <t>036540</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>26600</v>
+        <v>9320</v>
       </c>
       <c r="F5" t="n">
-        <v>3657.3904</v>
+        <v>9958.041999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>97286584.8</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>92808951.2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8.5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -612,29 +612,31 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>에이팩트</t>
+          <t>나노신소재</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>200470</t>
+          <t>121600</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>9320</v>
+        <v>57200</v>
       </c>
       <c r="F6" t="n">
-        <v>4724.7595</v>
+        <v>769.8384</v>
       </c>
       <c r="G6" t="n">
         <v>44034759</v>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>-5.3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -644,12 +646,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>하이브</t>
+          <t>예스티</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>352820</t>
+          <t>122640</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -658,30 +660,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>177500</v>
+        <v>26600</v>
       </c>
       <c r="F7" t="n">
-        <v>522.8673</v>
+        <v>3657.3904</v>
       </c>
       <c r="G7" t="n">
-        <v>92808951.2</v>
+        <v>97286584.8</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>에이팩트</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>200470</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -690,49 +692,47 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>15190</v>
+        <v>9320</v>
       </c>
       <c r="F8" t="n">
-        <v>6935.1909</v>
+        <v>4724.7595</v>
       </c>
       <c r="G8" t="n">
-        <v>105345550.5</v>
+        <v>44034759</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>윈팩</t>
+          <t>하이브</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>097800</t>
+          <t>352820</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3280</v>
+        <v>177500</v>
       </c>
       <c r="F9" t="n">
-        <v>14176.2933</v>
+        <v>522.8673</v>
       </c>
       <c r="G9" t="n">
-        <v>46498242</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-18.51</v>
-      </c>
+        <v>92808951.2</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -742,12 +742,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>나노신소재</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>121600</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -756,13 +756,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>60400</v>
+        <v>15190</v>
       </c>
       <c r="F10" t="n">
-        <v>769.8384</v>
+        <v>6935.1909</v>
       </c>
       <c r="G10" t="n">
-        <v>46498242</v>
+        <v>105345550.5</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>윈팩</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>097800</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -788,64 +788,64 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>169300</v>
+        <v>3280</v>
       </c>
       <c r="F11" t="n">
-        <v>622.2419</v>
+        <v>14176.2933</v>
       </c>
       <c r="G11" t="n">
-        <v>105345550.5</v>
+        <v>46498242</v>
       </c>
       <c r="H11" t="n">
-        <v>3.61</v>
+        <v>-18.51</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>나노신소재</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>121600</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>276000</v>
+        <v>60400</v>
       </c>
       <c r="F12" t="n">
-        <v>16.2128</v>
+        <v>769.8384</v>
       </c>
       <c r="G12" t="n">
-        <v>4474741.5</v>
+        <v>46498242</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>메쥬</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0088M0</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -854,16 +854,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>14390</v>
+        <v>169300</v>
       </c>
       <c r="F13" t="n">
-        <v>3192.997</v>
+        <v>622.2419</v>
       </c>
       <c r="G13" t="n">
-        <v>45947227.2</v>
+        <v>105345550.5</v>
       </c>
       <c r="H13" t="n">
-        <v>1.84</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="14">
@@ -874,12 +874,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -888,13 +888,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>164900</v>
+        <v>276000</v>
       </c>
       <c r="F14" t="n">
-        <v>20.0507</v>
+        <v>16.2128</v>
       </c>
       <c r="G14" t="n">
-        <v>3306361</v>
+        <v>4474741.5</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -906,29 +906,31 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>엠케이전자</t>
+          <t>메쥬</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>033160</t>
+          <t>0088M0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>20000</v>
+        <v>14390</v>
       </c>
       <c r="F15" t="n">
-        <v>5705.9581</v>
+        <v>3192.997</v>
       </c>
       <c r="G15" t="n">
-        <v>114119161</v>
-      </c>
-      <c r="H15" t="inlineStr"/>
+        <v>45947227.2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.84</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -938,27 +940,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SFA반도체</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>036540</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>11460</v>
+        <v>164900</v>
       </c>
       <c r="F16" t="n">
-        <v>1620.958</v>
+        <v>20.0507</v>
       </c>
       <c r="G16" t="n">
-        <v>18576179</v>
+        <v>3306361</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -970,31 +972,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>인바디</t>
+          <t>엠케이전자</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>041830</t>
+          <t>033160</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>52100</v>
+        <v>20000</v>
       </c>
       <c r="F17" t="n">
-        <v>1715</v>
+        <v>5705.9581</v>
       </c>
       <c r="G17" t="n">
-        <v>89351500</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-11.24</v>
-      </c>
+        <v>114119161</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1004,31 +1004,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>SFA반도체</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>089970</t>
+          <t>036540</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>67400</v>
+        <v>11460</v>
       </c>
       <c r="F18" t="n">
-        <v>2045</v>
+        <v>1620.958</v>
       </c>
       <c r="G18" t="n">
-        <v>137833000</v>
-      </c>
-      <c r="H18" t="n">
-        <v>37.55</v>
-      </c>
+        <v>18576179</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1038,29 +1036,31 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>윈팩</t>
+          <t>인바디</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>097800</t>
+          <t>041830</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4025</v>
+        <v>52100</v>
       </c>
       <c r="F19" t="n">
-        <v>14176.2933</v>
+        <v>1715</v>
       </c>
       <c r="G19" t="n">
-        <v>57059580.5</v>
-      </c>
-      <c r="H19" t="inlineStr"/>
+        <v>89351500</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-11.24</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1070,29 +1070,31 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>089970</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>92300</v>
+        <v>67400</v>
       </c>
       <c r="F20" t="n">
-        <v>17.6286</v>
+        <v>2045</v>
       </c>
       <c r="G20" t="n">
-        <v>1627115.2</v>
-      </c>
-      <c r="H20" t="inlineStr"/>
+        <v>137833000</v>
+      </c>
+      <c r="H20" t="n">
+        <v>37.55</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1102,31 +1104,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>윈팩</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>097800</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>92300</v>
+        <v>4025</v>
       </c>
       <c r="F21" t="n">
-        <v>1236.3939</v>
+        <v>14176.2933</v>
       </c>
       <c r="G21" t="n">
-        <v>114119161</v>
-      </c>
-      <c r="H21" t="n">
-        <v>19.61</v>
-      </c>
+        <v>57059580.5</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1136,27 +1136,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>27134.41</v>
+        <v>92300</v>
       </c>
       <c r="F22" t="n">
-        <v>2102.8495</v>
+        <v>17.6286</v>
       </c>
       <c r="G22" t="n">
-        <v>57059580.5</v>
+        <v>1627115.2</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1168,29 +1168,31 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>27134.41</v>
+        <v>92300</v>
       </c>
       <c r="F23" t="n">
-        <v>2102.8495</v>
+        <v>1236.3939</v>
       </c>
       <c r="G23" t="n">
-        <v>57059580.5</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
+        <v>114119161</v>
+      </c>
+      <c r="H23" t="n">
+        <v>19.61</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1200,12 +1202,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>에이치브이엠</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>295310</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1214,13 +1216,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>69700</v>
+        <v>27134.41</v>
       </c>
       <c r="F24" t="n">
-        <v>1637.2907</v>
+        <v>2102.8495</v>
       </c>
       <c r="G24" t="n">
-        <v>114119161</v>
+        <v>57059580.5</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1232,12 +1234,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1246,13 +1248,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>139200</v>
+        <v>27134.41</v>
       </c>
       <c r="F25" t="n">
-        <v>91.04859999999999</v>
+        <v>2102.8495</v>
       </c>
       <c r="G25" t="n">
-        <v>12673960.8</v>
+        <v>57059580.5</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1264,27 +1266,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>에이치브이엠</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>420770</t>
+          <t>295310</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>129300</v>
+        <v>69700</v>
       </c>
       <c r="F26" t="n">
-        <v>130.4079</v>
+        <v>1637.2907</v>
       </c>
       <c r="G26" t="n">
-        <v>16861739</v>
+        <v>114119161</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1296,12 +1298,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1310,77 +1312,77 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>183400</v>
+        <v>139200</v>
       </c>
       <c r="F27" t="n">
-        <v>9.241899999999999</v>
+        <v>91.04859999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>1694961</v>
+        <v>12673960.8</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>메쥬</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0088M0</t>
+          <t>420770</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>14130</v>
+        <v>129300</v>
       </c>
       <c r="F28" t="n">
-        <v>3247.997</v>
+        <v>130.4079</v>
       </c>
       <c r="G28" t="n">
-        <v>45894198</v>
+        <v>16861739</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>메쥬</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0088M0</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>14130</v>
+        <v>183400</v>
       </c>
       <c r="F29" t="n">
-        <v>55</v>
+        <v>9.241899999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>777150</v>
+        <v>1694961</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1392,31 +1394,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>롯데쇼핑</t>
+          <t>메쥬</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>023530</t>
+          <t>0088M0</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102200</v>
+        <v>14130</v>
       </c>
       <c r="F30" t="n">
-        <v>867</v>
+        <v>3247.997</v>
       </c>
       <c r="G30" t="n">
-        <v>88607400</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-11.36</v>
-      </c>
+        <v>45894198</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1426,31 +1426,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>메쥬</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>0088M0</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>13980</v>
+        <v>14130</v>
       </c>
       <c r="F31" t="n">
-        <v>6766</v>
+        <v>55</v>
       </c>
       <c r="G31" t="n">
-        <v>94588680</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-4.25</v>
-      </c>
+        <v>777150</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1460,29 +1458,31 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>롯데쇼핑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>023530</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>82900</v>
+        <v>102200</v>
       </c>
       <c r="F32" t="n">
-        <v>553.6091</v>
+        <v>867</v>
       </c>
       <c r="G32" t="n">
-        <v>45894198</v>
-      </c>
-      <c r="H32" t="inlineStr"/>
+        <v>88607400</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-11.36</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1492,78 +1492,78 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>125800</v>
+        <v>13980</v>
       </c>
       <c r="F33" t="n">
-        <v>728.773</v>
+        <v>6766</v>
       </c>
       <c r="G33" t="n">
-        <v>91679642.09999999</v>
-      </c>
-      <c r="H33" t="inlineStr"/>
+        <v>94588680</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-4.25</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>탑코미디어</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>134580</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3750</v>
+        <v>82900</v>
       </c>
       <c r="F34" t="n">
-        <v>12771</v>
+        <v>553.6091</v>
       </c>
       <c r="G34" t="n">
-        <v>47891250</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-7.06</v>
-      </c>
+        <v>45894198</v>
+      </c>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1572,62 +1572,64 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>72000</v>
+        <v>125800</v>
       </c>
       <c r="F35" t="n">
-        <v>665.1562</v>
+        <v>728.773</v>
       </c>
       <c r="G35" t="n">
-        <v>47891250</v>
+        <v>91679642.09999999</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>탑코미디어</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>134580</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>248500</v>
+        <v>3750</v>
       </c>
       <c r="F36" t="n">
-        <v>604</v>
+        <v>12771</v>
       </c>
       <c r="G36" t="n">
-        <v>150094000</v>
-      </c>
-      <c r="H36" t="inlineStr"/>
+        <v>47891250</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-7.06</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1636,13 +1638,13 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>147200</v>
+        <v>72000</v>
       </c>
       <c r="F37" t="n">
-        <v>672</v>
+        <v>665.1562</v>
       </c>
       <c r="G37" t="n">
-        <v>98918400</v>
+        <v>47891250</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1654,12 +1656,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>롯데쇼핑</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>023530</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1668,13 +1670,13 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>115300</v>
+        <v>248500</v>
       </c>
       <c r="F38" t="n">
-        <v>867</v>
+        <v>604</v>
       </c>
       <c r="G38" t="n">
-        <v>99965100</v>
+        <v>150094000</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1686,12 +1688,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SFA반도체</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>036540</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1700,13 +1702,13 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>8590</v>
+        <v>147200</v>
       </c>
       <c r="F39" t="n">
-        <v>11579</v>
+        <v>672</v>
       </c>
       <c r="G39" t="n">
-        <v>99463610</v>
+        <v>98918400</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1718,12 +1720,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>인바디</t>
+          <t>롯데쇼핑</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>041830</t>
+          <t>023530</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1732,13 +1734,13 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>58700</v>
+        <v>115300</v>
       </c>
       <c r="F40" t="n">
-        <v>1715</v>
+        <v>867</v>
       </c>
       <c r="G40" t="n">
-        <v>100670500</v>
+        <v>99965100</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1750,12 +1752,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>SFA반도체</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>089970</t>
+          <t>036540</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1764,13 +1766,13 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>49000</v>
+        <v>8590</v>
       </c>
       <c r="F41" t="n">
-        <v>2045</v>
+        <v>11579</v>
       </c>
       <c r="G41" t="n">
-        <v>100205000</v>
+        <v>99463610</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1782,12 +1784,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>인바디</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>041830</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1796,13 +1798,13 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>14600</v>
+        <v>58700</v>
       </c>
       <c r="F42" t="n">
-        <v>6766</v>
+        <v>1715</v>
       </c>
       <c r="G42" t="n">
-        <v>98783600</v>
+        <v>100670500</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1814,12 +1816,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>탑코미디어</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>134580</t>
+          <t>089970</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1828,13 +1830,13 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4035</v>
+        <v>49000</v>
       </c>
       <c r="F43" t="n">
-        <v>12771</v>
+        <v>2045</v>
       </c>
       <c r="G43" t="n">
-        <v>51530985</v>
+        <v>100205000</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
@@ -1846,12 +1848,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>420770</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1860,13 +1862,13 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>99100</v>
+        <v>14600</v>
       </c>
       <c r="F44" t="n">
-        <v>1013</v>
+        <v>6766</v>
       </c>
       <c r="G44" t="n">
-        <v>100388300</v>
+        <v>98783600</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1878,29 +1880,93 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>탑코미디어</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>134580</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>4035</v>
+      </c>
+      <c r="F45" t="n">
+        <v>12771</v>
+      </c>
+      <c r="G45" t="n">
+        <v>51530985</v>
+      </c>
+      <c r="H45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>기가비스</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>420770</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>99100</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1013</v>
+      </c>
+      <c r="G46" t="n">
+        <v>100388300</v>
+      </c>
+      <c r="H46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>달바글로벌</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>483650</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
         <v>163100</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F47" t="n">
         <v>613</v>
       </c>
-      <c r="G45" t="n">
+      <c r="G47" t="n">
         <v>99980300</v>
       </c>
-      <c r="H45" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/my_mp_history.xlsx
+++ b/docs/downloads/my_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,117 +473,115 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>나노엔텍</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>039860</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4865</v>
+        <v>24200</v>
       </c>
       <c r="F2" t="n">
-        <v>14879.8034</v>
+        <v>4205.699</v>
       </c>
       <c r="G2" t="n">
-        <v>72390243.59999999</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
+        <v>101777915.8</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-10.81</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>한선엔지니어링</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>452280</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>88300</v>
+        <v>13310</v>
       </c>
       <c r="F3" t="n">
-        <v>819.8216</v>
+        <v>7646.7255</v>
       </c>
       <c r="G3" t="n">
-        <v>72390243.59999999</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-30.63</v>
-      </c>
+        <v>101777915.8</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>엠케이전자</t>
+          <t>나노엔텍</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>033160</t>
+          <t>039860</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>17050</v>
+        <v>4865</v>
       </c>
       <c r="F4" t="n">
-        <v>5705.9581</v>
+        <v>14879.8034</v>
       </c>
       <c r="G4" t="n">
-        <v>97286584.8</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-14.75</v>
-      </c>
+        <v>72390243.59999999</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SFA반도체</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>036540</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -592,16 +590,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>9320</v>
+        <v>88300</v>
       </c>
       <c r="F5" t="n">
-        <v>9958.041999999999</v>
+        <v>819.8216</v>
       </c>
       <c r="G5" t="n">
-        <v>92808951.2</v>
+        <v>72390243.59999999</v>
       </c>
       <c r="H5" t="n">
-        <v>8.5</v>
+        <v>-30.63</v>
       </c>
     </row>
     <row r="6">
@@ -612,12 +610,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>나노신소재</t>
+          <t>엠케이전자</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>121600</t>
+          <t>033160</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -626,16 +624,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>57200</v>
+        <v>17050</v>
       </c>
       <c r="F6" t="n">
-        <v>769.8384</v>
+        <v>5705.9581</v>
       </c>
       <c r="G6" t="n">
-        <v>44034759</v>
+        <v>97286584.8</v>
       </c>
       <c r="H6" t="n">
-        <v>-5.3</v>
+        <v>-14.75</v>
       </c>
     </row>
     <row r="7">
@@ -646,29 +644,31 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>예스티</t>
+          <t>SFA반도체</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>122640</t>
+          <t>036540</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>26600</v>
+        <v>9320</v>
       </c>
       <c r="F7" t="n">
-        <v>3657.3904</v>
+        <v>9958.041999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>97286584.8</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
+        <v>92808951.2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>8.5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -678,29 +678,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>에이팩트</t>
+          <t>나노신소재</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>200470</t>
+          <t>121600</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>9320</v>
+        <v>57200</v>
       </c>
       <c r="F8" t="n">
-        <v>4724.7595</v>
+        <v>769.8384</v>
       </c>
       <c r="G8" t="n">
         <v>44034759</v>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>-5.3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -710,12 +712,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>하이브</t>
+          <t>예스티</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>352820</t>
+          <t>122640</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -724,30 +726,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>177500</v>
+        <v>26600</v>
       </c>
       <c r="F9" t="n">
-        <v>522.8673</v>
+        <v>3657.3904</v>
       </c>
       <c r="G9" t="n">
-        <v>92808951.2</v>
+        <v>97286584.8</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>에이팩트</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>200470</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -756,49 +758,47 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>15190</v>
+        <v>9320</v>
       </c>
       <c r="F10" t="n">
-        <v>6935.1909</v>
+        <v>4724.7595</v>
       </c>
       <c r="G10" t="n">
-        <v>105345550.5</v>
+        <v>44034759</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>윈팩</t>
+          <t>하이브</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>097800</t>
+          <t>352820</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3280</v>
+        <v>177500</v>
       </c>
       <c r="F11" t="n">
-        <v>14176.2933</v>
+        <v>522.8673</v>
       </c>
       <c r="G11" t="n">
-        <v>46498242</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-18.51</v>
-      </c>
+        <v>92808951.2</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -808,12 +808,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>나노신소재</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>121600</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -822,13 +822,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>60400</v>
+        <v>15190</v>
       </c>
       <c r="F12" t="n">
-        <v>769.8384</v>
+        <v>6935.1909</v>
       </c>
       <c r="G12" t="n">
-        <v>46498242</v>
+        <v>105345550.5</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -840,12 +840,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>윈팩</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>097800</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -854,64 +854,64 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>169300</v>
+        <v>3280</v>
       </c>
       <c r="F13" t="n">
-        <v>622.2419</v>
+        <v>14176.2933</v>
       </c>
       <c r="G13" t="n">
-        <v>105345550.5</v>
+        <v>46498242</v>
       </c>
       <c r="H13" t="n">
-        <v>3.61</v>
+        <v>-18.51</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>나노신소재</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>121600</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>276000</v>
+        <v>60400</v>
       </c>
       <c r="F14" t="n">
-        <v>16.2128</v>
+        <v>769.8384</v>
       </c>
       <c r="G14" t="n">
-        <v>4474741.5</v>
+        <v>46498242</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>메쥬</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0088M0</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -920,16 +920,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>14390</v>
+        <v>169300</v>
       </c>
       <c r="F15" t="n">
-        <v>3192.997</v>
+        <v>622.2419</v>
       </c>
       <c r="G15" t="n">
-        <v>45947227.2</v>
+        <v>105345550.5</v>
       </c>
       <c r="H15" t="n">
-        <v>1.84</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="16">
@@ -940,12 +940,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -954,13 +954,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>164900</v>
+        <v>276000</v>
       </c>
       <c r="F16" t="n">
-        <v>20.0507</v>
+        <v>16.2128</v>
       </c>
       <c r="G16" t="n">
-        <v>3306361</v>
+        <v>4474741.5</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -972,29 +972,31 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>엠케이전자</t>
+          <t>메쥬</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>033160</t>
+          <t>0088M0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>20000</v>
+        <v>14390</v>
       </c>
       <c r="F17" t="n">
-        <v>5705.9581</v>
+        <v>3192.997</v>
       </c>
       <c r="G17" t="n">
-        <v>114119161</v>
-      </c>
-      <c r="H17" t="inlineStr"/>
+        <v>45947227.2</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.84</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1004,27 +1006,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SFA반도체</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>036540</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>11460</v>
+        <v>164900</v>
       </c>
       <c r="F18" t="n">
-        <v>1620.958</v>
+        <v>20.0507</v>
       </c>
       <c r="G18" t="n">
-        <v>18576179</v>
+        <v>3306361</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1036,31 +1038,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>인바디</t>
+          <t>엠케이전자</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>041830</t>
+          <t>033160</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>52100</v>
+        <v>20000</v>
       </c>
       <c r="F19" t="n">
-        <v>1715</v>
+        <v>5705.9581</v>
       </c>
       <c r="G19" t="n">
-        <v>89351500</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-11.24</v>
-      </c>
+        <v>114119161</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1070,31 +1070,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>SFA반도체</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>089970</t>
+          <t>036540</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>67400</v>
+        <v>11460</v>
       </c>
       <c r="F20" t="n">
-        <v>2045</v>
+        <v>1620.958</v>
       </c>
       <c r="G20" t="n">
-        <v>137833000</v>
-      </c>
-      <c r="H20" t="n">
-        <v>37.55</v>
-      </c>
+        <v>18576179</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1104,29 +1102,31 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>윈팩</t>
+          <t>인바디</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>097800</t>
+          <t>041830</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4025</v>
+        <v>52100</v>
       </c>
       <c r="F21" t="n">
-        <v>14176.2933</v>
+        <v>1715</v>
       </c>
       <c r="G21" t="n">
-        <v>57059580.5</v>
-      </c>
-      <c r="H21" t="inlineStr"/>
+        <v>89351500</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-11.24</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1136,29 +1136,31 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>089970</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>92300</v>
+        <v>67400</v>
       </c>
       <c r="F22" t="n">
-        <v>17.6286</v>
+        <v>2045</v>
       </c>
       <c r="G22" t="n">
-        <v>1627115.2</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>137833000</v>
+      </c>
+      <c r="H22" t="n">
+        <v>37.55</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1168,31 +1170,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>윈팩</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>097800</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>92300</v>
+        <v>4025</v>
       </c>
       <c r="F23" t="n">
-        <v>1236.3939</v>
+        <v>14176.2933</v>
       </c>
       <c r="G23" t="n">
-        <v>114119161</v>
-      </c>
-      <c r="H23" t="n">
-        <v>19.61</v>
-      </c>
+        <v>57059580.5</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1202,27 +1202,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>27134.41</v>
+        <v>92300</v>
       </c>
       <c r="F24" t="n">
-        <v>2102.8495</v>
+        <v>17.6286</v>
       </c>
       <c r="G24" t="n">
-        <v>57059580.5</v>
+        <v>1627115.2</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1234,29 +1234,31 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>27134.41</v>
+        <v>92300</v>
       </c>
       <c r="F25" t="n">
-        <v>2102.8495</v>
+        <v>1236.3939</v>
       </c>
       <c r="G25" t="n">
-        <v>57059580.5</v>
-      </c>
-      <c r="H25" t="inlineStr"/>
+        <v>114119161</v>
+      </c>
+      <c r="H25" t="n">
+        <v>19.61</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1266,12 +1268,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>에이치브이엠</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>295310</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1280,13 +1282,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>69700</v>
+        <v>27134.41</v>
       </c>
       <c r="F26" t="n">
-        <v>1637.2907</v>
+        <v>2102.8495</v>
       </c>
       <c r="G26" t="n">
-        <v>114119161</v>
+        <v>57059580.5</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1298,12 +1300,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1312,13 +1314,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>139200</v>
+        <v>27134.41</v>
       </c>
       <c r="F27" t="n">
-        <v>91.04859999999999</v>
+        <v>2102.8495</v>
       </c>
       <c r="G27" t="n">
-        <v>12673960.8</v>
+        <v>57059580.5</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1330,27 +1332,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>에이치브이엠</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>420770</t>
+          <t>295310</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>129300</v>
+        <v>69700</v>
       </c>
       <c r="F28" t="n">
-        <v>130.4079</v>
+        <v>1637.2907</v>
       </c>
       <c r="G28" t="n">
-        <v>16861739</v>
+        <v>114119161</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1362,12 +1364,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1376,77 +1378,77 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>183400</v>
+        <v>139200</v>
       </c>
       <c r="F29" t="n">
-        <v>9.241899999999999</v>
+        <v>91.04859999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>1694961</v>
+        <v>12673960.8</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>메쥬</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0088M0</t>
+          <t>420770</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>14130</v>
+        <v>129300</v>
       </c>
       <c r="F30" t="n">
-        <v>3247.997</v>
+        <v>130.4079</v>
       </c>
       <c r="G30" t="n">
-        <v>45894198</v>
+        <v>16861739</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>메쥬</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0088M0</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>14130</v>
+        <v>183400</v>
       </c>
       <c r="F31" t="n">
-        <v>55</v>
+        <v>9.241899999999999</v>
       </c>
       <c r="G31" t="n">
-        <v>777150</v>
+        <v>1694961</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1458,31 +1460,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>롯데쇼핑</t>
+          <t>메쥬</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>023530</t>
+          <t>0088M0</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102200</v>
+        <v>14130</v>
       </c>
       <c r="F32" t="n">
-        <v>867</v>
+        <v>3247.997</v>
       </c>
       <c r="G32" t="n">
-        <v>88607400</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-11.36</v>
-      </c>
+        <v>45894198</v>
+      </c>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1492,31 +1492,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>메쥬</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>0088M0</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>13980</v>
+        <v>14130</v>
       </c>
       <c r="F33" t="n">
-        <v>6766</v>
+        <v>55</v>
       </c>
       <c r="G33" t="n">
-        <v>94588680</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-4.25</v>
-      </c>
+        <v>777150</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1526,29 +1524,31 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>롯데쇼핑</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>023530</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>82900</v>
+        <v>102200</v>
       </c>
       <c r="F34" t="n">
-        <v>553.6091</v>
+        <v>867</v>
       </c>
       <c r="G34" t="n">
-        <v>45894198</v>
-      </c>
-      <c r="H34" t="inlineStr"/>
+        <v>88607400</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-11.36</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1558,78 +1558,78 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>125800</v>
+        <v>13980</v>
       </c>
       <c r="F35" t="n">
-        <v>728.773</v>
+        <v>6766</v>
       </c>
       <c r="G35" t="n">
-        <v>91679642.09999999</v>
-      </c>
-      <c r="H35" t="inlineStr"/>
+        <v>94588680</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-4.25</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>탑코미디어</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>134580</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3750</v>
+        <v>82900</v>
       </c>
       <c r="F36" t="n">
-        <v>12771</v>
+        <v>553.6091</v>
       </c>
       <c r="G36" t="n">
-        <v>47891250</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-7.06</v>
-      </c>
+        <v>45894198</v>
+      </c>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1638,62 +1638,64 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>72000</v>
+        <v>125800</v>
       </c>
       <c r="F37" t="n">
-        <v>665.1562</v>
+        <v>728.773</v>
       </c>
       <c r="G37" t="n">
-        <v>47891250</v>
+        <v>91679642.09999999</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>탑코미디어</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>134580</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>248500</v>
+        <v>3750</v>
       </c>
       <c r="F38" t="n">
-        <v>604</v>
+        <v>12771</v>
       </c>
       <c r="G38" t="n">
-        <v>150094000</v>
-      </c>
-      <c r="H38" t="inlineStr"/>
+        <v>47891250</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-7.06</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1702,13 +1704,13 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>147200</v>
+        <v>72000</v>
       </c>
       <c r="F39" t="n">
-        <v>672</v>
+        <v>665.1562</v>
       </c>
       <c r="G39" t="n">
-        <v>98918400</v>
+        <v>47891250</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1720,12 +1722,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>롯데쇼핑</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>023530</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1734,13 +1736,13 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>115300</v>
+        <v>248500</v>
       </c>
       <c r="F40" t="n">
-        <v>867</v>
+        <v>604</v>
       </c>
       <c r="G40" t="n">
-        <v>99965100</v>
+        <v>150094000</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1752,12 +1754,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SFA반도체</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>036540</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1766,13 +1768,13 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>8590</v>
+        <v>147200</v>
       </c>
       <c r="F41" t="n">
-        <v>11579</v>
+        <v>672</v>
       </c>
       <c r="G41" t="n">
-        <v>99463610</v>
+        <v>98918400</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1784,12 +1786,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>인바디</t>
+          <t>롯데쇼핑</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>041830</t>
+          <t>023530</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1798,13 +1800,13 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>58700</v>
+        <v>115300</v>
       </c>
       <c r="F42" t="n">
-        <v>1715</v>
+        <v>867</v>
       </c>
       <c r="G42" t="n">
-        <v>100670500</v>
+        <v>99965100</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1816,12 +1818,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>SFA반도체</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>089970</t>
+          <t>036540</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1830,13 +1832,13 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>49000</v>
+        <v>8590</v>
       </c>
       <c r="F43" t="n">
-        <v>2045</v>
+        <v>11579</v>
       </c>
       <c r="G43" t="n">
-        <v>100205000</v>
+        <v>99463610</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
@@ -1848,12 +1850,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>인바디</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>041830</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1862,13 +1864,13 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>14600</v>
+        <v>58700</v>
       </c>
       <c r="F44" t="n">
-        <v>6766</v>
+        <v>1715</v>
       </c>
       <c r="G44" t="n">
-        <v>98783600</v>
+        <v>100670500</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1880,12 +1882,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>탑코미디어</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>134580</t>
+          <t>089970</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1894,13 +1896,13 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4035</v>
+        <v>49000</v>
       </c>
       <c r="F45" t="n">
-        <v>12771</v>
+        <v>2045</v>
       </c>
       <c r="G45" t="n">
-        <v>51530985</v>
+        <v>100205000</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1912,12 +1914,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>420770</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1926,13 +1928,13 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>99100</v>
+        <v>14600</v>
       </c>
       <c r="F46" t="n">
-        <v>1013</v>
+        <v>6766</v>
       </c>
       <c r="G46" t="n">
-        <v>100388300</v>
+        <v>98783600</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1944,29 +1946,93 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>탑코미디어</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>134580</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>4035</v>
+      </c>
+      <c r="F47" t="n">
+        <v>12771</v>
+      </c>
+      <c r="G47" t="n">
+        <v>51530985</v>
+      </c>
+      <c r="H47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>기가비스</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>420770</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>99100</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1013</v>
+      </c>
+      <c r="G48" t="n">
+        <v>100388300</v>
+      </c>
+      <c r="H48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>달바글로벌</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>483650</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
         <v>163100</v>
       </c>
-      <c r="F47" t="n">
+      <c r="F49" t="n">
         <v>613</v>
       </c>
-      <c r="G47" t="n">
+      <c r="G49" t="n">
         <v>99980300</v>
       </c>
-      <c r="H47" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
